--- a/ResourcesBD/UserBulkUpload.xlsx
+++ b/ResourcesBD/UserBulkUpload.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="127">
   <si>
     <t>Code*</t>
   </si>
@@ -382,6 +382,24 @@
   </si>
   <si>
     <t>48007907497956776</t>
+  </si>
+  <si>
+    <t>User_4359A</t>
+  </si>
+  <si>
+    <t>Auto_FEBE8</t>
+  </si>
+  <si>
+    <t>51091436477787881</t>
+  </si>
+  <si>
+    <t>User_03FEB</t>
+  </si>
+  <si>
+    <t>Auto_AC240</t>
+  </si>
+  <si>
+    <t>65016883869987570</t>
   </si>
 </sst>
 </file>
@@ -777,13 +795,13 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>15</v>
@@ -824,13 +842,13 @@
     </row>
     <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>

--- a/ResourcesBD/UserBulkUpload.xlsx
+++ b/ResourcesBD/UserBulkUpload.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="139">
   <si>
     <t>Code*</t>
   </si>
@@ -400,6 +400,42 @@
   </si>
   <si>
     <t>65016883869987570</t>
+  </si>
+  <si>
+    <t>User_A856F</t>
+  </si>
+  <si>
+    <t>Auto_BDE04</t>
+  </si>
+  <si>
+    <t>72960516028075262</t>
+  </si>
+  <si>
+    <t>User_2A9B4</t>
+  </si>
+  <si>
+    <t>Auto_210A3</t>
+  </si>
+  <si>
+    <t>47315910554249175</t>
+  </si>
+  <si>
+    <t>User_CF1E5</t>
+  </si>
+  <si>
+    <t>Auto_FB32B</t>
+  </si>
+  <si>
+    <t>37704819628322661</t>
+  </si>
+  <si>
+    <t>User_ABF6F</t>
+  </si>
+  <si>
+    <t>Auto_CA573</t>
+  </si>
+  <si>
+    <t>19462722272864282</t>
   </si>
 </sst>
 </file>
@@ -795,13 +831,13 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>15</v>
@@ -842,13 +878,13 @@
     </row>
     <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>

--- a/ResourcesBD/UserBulkUpload.xlsx
+++ b/ResourcesBD/UserBulkUpload.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="175">
   <si>
     <t>Code*</t>
   </si>
@@ -436,6 +436,114 @@
   </si>
   <si>
     <t>19462722272864282</t>
+  </si>
+  <si>
+    <t>User_7B529</t>
+  </si>
+  <si>
+    <t>Auto_48126</t>
+  </si>
+  <si>
+    <t>76617272358362382</t>
+  </si>
+  <si>
+    <t>User_508E1</t>
+  </si>
+  <si>
+    <t>Auto_6E2F2</t>
+  </si>
+  <si>
+    <t>58741080710950603</t>
+  </si>
+  <si>
+    <t>User_CA77B</t>
+  </si>
+  <si>
+    <t>Auto_E16CF</t>
+  </si>
+  <si>
+    <t>36104430049920967</t>
+  </si>
+  <si>
+    <t>User_24A8B</t>
+  </si>
+  <si>
+    <t>Auto_9432A</t>
+  </si>
+  <si>
+    <t>89429719930611138</t>
+  </si>
+  <si>
+    <t>User_BF2C7</t>
+  </si>
+  <si>
+    <t>Auto_4A306</t>
+  </si>
+  <si>
+    <t>92093753469549989</t>
+  </si>
+  <si>
+    <t>User_0F1C7</t>
+  </si>
+  <si>
+    <t>Auto_D2CE5</t>
+  </si>
+  <si>
+    <t>79341118575930279</t>
+  </si>
+  <si>
+    <t>User_9EFEF</t>
+  </si>
+  <si>
+    <t>Auto_2DD2D</t>
+  </si>
+  <si>
+    <t>73623614700894013</t>
+  </si>
+  <si>
+    <t>User_013A4</t>
+  </si>
+  <si>
+    <t>Auto_2B764</t>
+  </si>
+  <si>
+    <t>72316957395559126</t>
+  </si>
+  <si>
+    <t>User_D6F7C</t>
+  </si>
+  <si>
+    <t>Auto_D1472</t>
+  </si>
+  <si>
+    <t>84290003068155919</t>
+  </si>
+  <si>
+    <t>User_044B0</t>
+  </si>
+  <si>
+    <t>Auto_6F5CB</t>
+  </si>
+  <si>
+    <t>13177526848536946</t>
+  </si>
+  <si>
+    <t>User_5B65D</t>
+  </si>
+  <si>
+    <t>Auto_92958</t>
+  </si>
+  <si>
+    <t>25841345605785045</t>
+  </si>
+  <si>
+    <t>User_C471D</t>
+  </si>
+  <si>
+    <t>Auto_24FF7</t>
+  </si>
+  <si>
+    <t>35939888564919814</t>
   </si>
 </sst>
 </file>
@@ -831,13 +939,13 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>15</v>
@@ -878,13 +986,13 @@
     </row>
     <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>

--- a/ResourcesBD/UserBulkUpload.xlsx
+++ b/ResourcesBD/UserBulkUpload.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="313">
   <si>
     <t>Code*</t>
   </si>
@@ -544,6 +544,420 @@
   </si>
   <si>
     <t>35939888564919814</t>
+  </si>
+  <si>
+    <t>User_BD372</t>
+  </si>
+  <si>
+    <t>Auto_BEFE0</t>
+  </si>
+  <si>
+    <t>75814079116920597</t>
+  </si>
+  <si>
+    <t>User_92AA4</t>
+  </si>
+  <si>
+    <t>Auto_3CCBA</t>
+  </si>
+  <si>
+    <t>15795477649317785</t>
+  </si>
+  <si>
+    <t>User_03C07</t>
+  </si>
+  <si>
+    <t>Auto_A6E3C</t>
+  </si>
+  <si>
+    <t>26398445691929731</t>
+  </si>
+  <si>
+    <t>User_A566A</t>
+  </si>
+  <si>
+    <t>Auto_6DEE7</t>
+  </si>
+  <si>
+    <t>24133768032801004</t>
+  </si>
+  <si>
+    <t>User_8BB84</t>
+  </si>
+  <si>
+    <t>Auto_D5383</t>
+  </si>
+  <si>
+    <t>21537361707216564</t>
+  </si>
+  <si>
+    <t>User_818E0</t>
+  </si>
+  <si>
+    <t>Auto_DEF9D</t>
+  </si>
+  <si>
+    <t>95350723508678378</t>
+  </si>
+  <si>
+    <t>User_82FEA</t>
+  </si>
+  <si>
+    <t>Auto_00755</t>
+  </si>
+  <si>
+    <t>35599144018335441</t>
+  </si>
+  <si>
+    <t>User_B1FF2</t>
+  </si>
+  <si>
+    <t>Auto_06D91</t>
+  </si>
+  <si>
+    <t>71559783045930201</t>
+  </si>
+  <si>
+    <t>User_EBD8A</t>
+  </si>
+  <si>
+    <t>Auto_D8B8A</t>
+  </si>
+  <si>
+    <t>14747993460218694</t>
+  </si>
+  <si>
+    <t>User_1059D</t>
+  </si>
+  <si>
+    <t>Auto_2CB62</t>
+  </si>
+  <si>
+    <t>77327892103374278</t>
+  </si>
+  <si>
+    <t>User_3A5BC</t>
+  </si>
+  <si>
+    <t>Auto_32F88</t>
+  </si>
+  <si>
+    <t>26100976626702739</t>
+  </si>
+  <si>
+    <t>User_14307</t>
+  </si>
+  <si>
+    <t>Auto_B8E8F</t>
+  </si>
+  <si>
+    <t>38334230061700031</t>
+  </si>
+  <si>
+    <t>User_8B5E6</t>
+  </si>
+  <si>
+    <t>Auto_FD11E</t>
+  </si>
+  <si>
+    <t>97964104523164747</t>
+  </si>
+  <si>
+    <t>User_73D36</t>
+  </si>
+  <si>
+    <t>Auto_9F40F</t>
+  </si>
+  <si>
+    <t>48903535583401757</t>
+  </si>
+  <si>
+    <t>User_1ED42</t>
+  </si>
+  <si>
+    <t>Auto_24DEB</t>
+  </si>
+  <si>
+    <t>55710345749614410</t>
+  </si>
+  <si>
+    <t>User_18E5A</t>
+  </si>
+  <si>
+    <t>Auto_70FFD</t>
+  </si>
+  <si>
+    <t>97680968488955600</t>
+  </si>
+  <si>
+    <t>User_44C1D</t>
+  </si>
+  <si>
+    <t>Auto_E6202</t>
+  </si>
+  <si>
+    <t>22778140374242684</t>
+  </si>
+  <si>
+    <t>User_57D66</t>
+  </si>
+  <si>
+    <t>Auto_95007</t>
+  </si>
+  <si>
+    <t>58908612103969704</t>
+  </si>
+  <si>
+    <t>User_3ACE9</t>
+  </si>
+  <si>
+    <t>Auto_1FE15</t>
+  </si>
+  <si>
+    <t>45042185979190621</t>
+  </si>
+  <si>
+    <t>User_4D89B</t>
+  </si>
+  <si>
+    <t>Auto_FAC92</t>
+  </si>
+  <si>
+    <t>19860844179171696</t>
+  </si>
+  <si>
+    <t>User_BEB42</t>
+  </si>
+  <si>
+    <t>Auto_2D74B</t>
+  </si>
+  <si>
+    <t>71748307796761971</t>
+  </si>
+  <si>
+    <t>User_D0521</t>
+  </si>
+  <si>
+    <t>Auto_8BCF8</t>
+  </si>
+  <si>
+    <t>78208100463660215</t>
+  </si>
+  <si>
+    <t>User_2ADFD</t>
+  </si>
+  <si>
+    <t>Auto_BF0DC</t>
+  </si>
+  <si>
+    <t>98842135659868297</t>
+  </si>
+  <si>
+    <t>User_641AF</t>
+  </si>
+  <si>
+    <t>Auto_8666F</t>
+  </si>
+  <si>
+    <t>61632554584833769</t>
+  </si>
+  <si>
+    <t>User_A92D9</t>
+  </si>
+  <si>
+    <t>Auto_A92FF</t>
+  </si>
+  <si>
+    <t>10733032387115545</t>
+  </si>
+  <si>
+    <t>User_FB990</t>
+  </si>
+  <si>
+    <t>Auto_8EB25</t>
+  </si>
+  <si>
+    <t>60918253103416757</t>
+  </si>
+  <si>
+    <t>User_09A18</t>
+  </si>
+  <si>
+    <t>Auto_D81F7</t>
+  </si>
+  <si>
+    <t>85057619819401756</t>
+  </si>
+  <si>
+    <t>User_38049</t>
+  </si>
+  <si>
+    <t>Auto_05CC0</t>
+  </si>
+  <si>
+    <t>64781718062848480</t>
+  </si>
+  <si>
+    <t>User_592BE</t>
+  </si>
+  <si>
+    <t>Auto_7DA08</t>
+  </si>
+  <si>
+    <t>52829924128379821</t>
+  </si>
+  <si>
+    <t>User_8B9AB</t>
+  </si>
+  <si>
+    <t>Auto_0204A</t>
+  </si>
+  <si>
+    <t>29519326076196951</t>
+  </si>
+  <si>
+    <t>User_F3E39</t>
+  </si>
+  <si>
+    <t>Auto_049D1</t>
+  </si>
+  <si>
+    <t>11901377287923622</t>
+  </si>
+  <si>
+    <t>User_969B7</t>
+  </si>
+  <si>
+    <t>Auto_B99ED</t>
+  </si>
+  <si>
+    <t>54484022542736702</t>
+  </si>
+  <si>
+    <t>User_662E8</t>
+  </si>
+  <si>
+    <t>Auto_36D9E</t>
+  </si>
+  <si>
+    <t>57598604288839839</t>
+  </si>
+  <si>
+    <t>User_37387</t>
+  </si>
+  <si>
+    <t>Auto_67BF7</t>
+  </si>
+  <si>
+    <t>73121791868039538</t>
+  </si>
+  <si>
+    <t>User_DFF6D</t>
+  </si>
+  <si>
+    <t>Auto_16F08</t>
+  </si>
+  <si>
+    <t>53268905196468630</t>
+  </si>
+  <si>
+    <t>User_258CF</t>
+  </si>
+  <si>
+    <t>Auto_80872</t>
+  </si>
+  <si>
+    <t>95208005162790910</t>
+  </si>
+  <si>
+    <t>User_95BDB</t>
+  </si>
+  <si>
+    <t>Auto_41451</t>
+  </si>
+  <si>
+    <t>48459856762200891</t>
+  </si>
+  <si>
+    <t>User_FF477</t>
+  </si>
+  <si>
+    <t>Auto_E576B</t>
+  </si>
+  <si>
+    <t>33011210385252257</t>
+  </si>
+  <si>
+    <t>User_58373</t>
+  </si>
+  <si>
+    <t>Auto_D860A</t>
+  </si>
+  <si>
+    <t>30095000105982726</t>
+  </si>
+  <si>
+    <t>User_081D2</t>
+  </si>
+  <si>
+    <t>Auto_A2B77</t>
+  </si>
+  <si>
+    <t>22578624091388200</t>
+  </si>
+  <si>
+    <t>User_3F81A</t>
+  </si>
+  <si>
+    <t>Auto_E2692</t>
+  </si>
+  <si>
+    <t>38220629095843111</t>
+  </si>
+  <si>
+    <t>User_7708D</t>
+  </si>
+  <si>
+    <t>Auto_EC3EA</t>
+  </si>
+  <si>
+    <t>87533437513115992</t>
+  </si>
+  <si>
+    <t>User_BE404</t>
+  </si>
+  <si>
+    <t>Auto_609D2</t>
+  </si>
+  <si>
+    <t>49884437631467750</t>
+  </si>
+  <si>
+    <t>User_B62FF</t>
+  </si>
+  <si>
+    <t>Auto_22CF8</t>
+  </si>
+  <si>
+    <t>91729105603532698</t>
+  </si>
+  <si>
+    <t>User_BBF8C</t>
+  </si>
+  <si>
+    <t>Auto_F33D9</t>
+  </si>
+  <si>
+    <t>79091145698735933</t>
+  </si>
+  <si>
+    <t>User_4DBC5</t>
+  </si>
+  <si>
+    <t>Auto_69494</t>
+  </si>
+  <si>
+    <t>45305637916675359</t>
   </si>
 </sst>
 </file>
@@ -939,13 +1353,13 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>169</v>
+        <v>307</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>170</v>
+        <v>308</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>171</v>
+        <v>309</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>15</v>
@@ -986,13 +1400,13 @@
     </row>
     <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>172</v>
+        <v>310</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>173</v>
+        <v>311</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>174</v>
+        <v>312</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>

--- a/ResourcesBD/UserBulkUpload.xlsx
+++ b/ResourcesBD/UserBulkUpload.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="373">
   <si>
     <t>Code*</t>
   </si>
@@ -958,6 +958,186 @@
   </si>
   <si>
     <t>45305637916675359</t>
+  </si>
+  <si>
+    <t>User_E7035</t>
+  </si>
+  <si>
+    <t>Auto_2546F</t>
+  </si>
+  <si>
+    <t>77689411550387525</t>
+  </si>
+  <si>
+    <t>User_D2149</t>
+  </si>
+  <si>
+    <t>Auto_55F77</t>
+  </si>
+  <si>
+    <t>63278154799626359</t>
+  </si>
+  <si>
+    <t>User_A8050</t>
+  </si>
+  <si>
+    <t>Auto_47B3E</t>
+  </si>
+  <si>
+    <t>21275745163667056</t>
+  </si>
+  <si>
+    <t>User_28B1D</t>
+  </si>
+  <si>
+    <t>Auto_A6B08</t>
+  </si>
+  <si>
+    <t>59863473814036952</t>
+  </si>
+  <si>
+    <t>User_8B3D7</t>
+  </si>
+  <si>
+    <t>Auto_9C9EB</t>
+  </si>
+  <si>
+    <t>65618448704946267</t>
+  </si>
+  <si>
+    <t>User_D1E71</t>
+  </si>
+  <si>
+    <t>Auto_6F231</t>
+  </si>
+  <si>
+    <t>78401657784526626</t>
+  </si>
+  <si>
+    <t>User_546EB</t>
+  </si>
+  <si>
+    <t>Auto_27E39</t>
+  </si>
+  <si>
+    <t>50281897156556391</t>
+  </si>
+  <si>
+    <t>User_5091B</t>
+  </si>
+  <si>
+    <t>Auto_55B72</t>
+  </si>
+  <si>
+    <t>57913344732467671</t>
+  </si>
+  <si>
+    <t>User_F0937</t>
+  </si>
+  <si>
+    <t>Auto_090E4</t>
+  </si>
+  <si>
+    <t>70074434395415235</t>
+  </si>
+  <si>
+    <t>User_5D415</t>
+  </si>
+  <si>
+    <t>Auto_2B0D4</t>
+  </si>
+  <si>
+    <t>36960795338199006</t>
+  </si>
+  <si>
+    <t>User_ED654</t>
+  </si>
+  <si>
+    <t>Auto_CEB8C</t>
+  </si>
+  <si>
+    <t>62217524839182651</t>
+  </si>
+  <si>
+    <t>User_73F55</t>
+  </si>
+  <si>
+    <t>Auto_837F1</t>
+  </si>
+  <si>
+    <t>45174554986361446</t>
+  </si>
+  <si>
+    <t>User_DA4C0</t>
+  </si>
+  <si>
+    <t>Auto_24444</t>
+  </si>
+  <si>
+    <t>38501288767848269</t>
+  </si>
+  <si>
+    <t>User_ED148</t>
+  </si>
+  <si>
+    <t>Auto_5CCE8</t>
+  </si>
+  <si>
+    <t>42377499371196463</t>
+  </si>
+  <si>
+    <t>User_40C72</t>
+  </si>
+  <si>
+    <t>Auto_23BCB</t>
+  </si>
+  <si>
+    <t>81647479507217350</t>
+  </si>
+  <si>
+    <t>User_D7030</t>
+  </si>
+  <si>
+    <t>Auto_8C567</t>
+  </si>
+  <si>
+    <t>82557611969348657</t>
+  </si>
+  <si>
+    <t>User_42DC8</t>
+  </si>
+  <si>
+    <t>Auto_D608B</t>
+  </si>
+  <si>
+    <t>70638235642995497</t>
+  </si>
+  <si>
+    <t>User_EC913</t>
+  </si>
+  <si>
+    <t>Auto_C731A</t>
+  </si>
+  <si>
+    <t>21411388052390556</t>
+  </si>
+  <si>
+    <t>User_927F0</t>
+  </si>
+  <si>
+    <t>Auto_6FB81</t>
+  </si>
+  <si>
+    <t>62782182427627626</t>
+  </si>
+  <si>
+    <t>User_825C3</t>
+  </si>
+  <si>
+    <t>Auto_C5C5D</t>
+  </si>
+  <si>
+    <t>20661643786549620</t>
   </si>
 </sst>
 </file>
@@ -1353,13 +1533,13 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>307</v>
+        <v>367</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>308</v>
+        <v>368</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>309</v>
+        <v>369</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>15</v>
@@ -1400,13 +1580,13 @@
     </row>
     <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>311</v>
+        <v>371</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>312</v>
+        <v>372</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
